--- a/data/trans_orig/IP33-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP33-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53181</t>
+          <t>53403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68506</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61195</t>
+          <t>61268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73548</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>119540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138332</t>
+          <t>138410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>26083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>43967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44583</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>69102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359765</t>
+          <t>360499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380413</t>
+          <t>379776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404557</t>
+          <t>403797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428088</t>
+          <t>428130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>772418</t>
+          <t>771010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>802283</t>
+          <t>800874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141833</t>
+          <t>141583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156243</t>
+          <t>156455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129247</t>
+          <t>128899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143164</t>
+          <t>143357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>276156</t>
+          <t>276193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296948</t>
+          <t>296158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,82 +2794,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12985</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>19522</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>29010</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>21137</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>37957</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>12985</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>8438</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>29010</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>21119</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>38971</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62719</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>85955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116114</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>566588</t>
+          <t>564877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>596165</t>
+          <t>594431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606269</t>
+          <t>604551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635390</t>
+          <t>635215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1183118</t>
+          <t>1175933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1224746</t>
+          <t>1220337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75117</t>
+          <t>74900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57914</t>
+          <t>57594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71458</t>
+          <t>71470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124324</t>
+          <t>124178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143655</t>
+          <t>144010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41605</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64053</t>
+          <t>64518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32858</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79058</t>
+          <t>79153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>109526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345692</t>
+          <t>344342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374222</t>
+          <t>372314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398187</t>
+          <t>398652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424577</t>
+          <t>426124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751528</t>
+          <t>752736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>791229</t>
+          <t>790860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>43989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138275</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152226</t>
+          <t>152188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134288</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150926</t>
+          <t>151476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277564</t>
+          <t>277303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299562</t>
+          <t>299422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39208</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42723</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>65853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55691</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67080</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58350</t>
+          <t>56886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86566</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131978</t>
+          <t>132166</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170520</t>
+          <t>173283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556665</t>
+          <t>558042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>591460</t>
+          <t>591356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>602224</t>
+          <t>601693</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>637301</t>
+          <t>636581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1171688</t>
+          <t>1168206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1219759</t>
+          <t>1219205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50996</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81672</t>
+          <t>80675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97996</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34250</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23041</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72607</t>
+          <t>72444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98140</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>71503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97371</t>
+          <t>99376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>150855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188584</t>
+          <t>189017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327118</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357275</t>
+          <t>359375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343136</t>
+          <t>343512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374114</t>
+          <t>375742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678599</t>
+          <t>678598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723317</t>
+          <t>721335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34307</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41707</t>
+          <t>42273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120068</t>
+          <t>121103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139071</t>
+          <t>139458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138200</t>
+          <t>136838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156426</t>
+          <t>156368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264962</t>
+          <t>264829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291455</t>
+          <t>290325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>78815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66969</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105056</t>
+          <t>102944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136283</t>
+          <t>137340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>103168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137988</t>
+          <t>137808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217216</t>
+          <t>217136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>264103</t>
+          <t>263803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>495563</t>
+          <t>495523</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>533920</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>532673</t>
+          <t>533092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>570164</t>
+          <t>572240</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1040893</t>
+          <t>1040888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1096709</t>
+          <t>1095270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35581</t>
+          <t>35607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>72109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91389</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56156</t>
+          <t>58382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,47 +10455,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>59553</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>45261</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>85992</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>59553</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>44166</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>80198</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32004</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>49390</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86670</t>
+          <t>86897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66882</t>
+          <t>67537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122459</t>
+          <t>115957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131947</t>
+          <t>131522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188563</t>
+          <t>188113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322943</t>
+          <t>323222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365328</t>
+          <t>366849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331949</t>
+          <t>334982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383597</t>
+          <t>386444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671608</t>
+          <t>671078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>737373</t>
+          <t>737534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,47 +11328,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>26147</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18276</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>36996</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>26147</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>17287</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30737</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111885</t>
+          <t>111687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128012</t>
+          <t>128233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>132267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154052</t>
+          <t>153618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250961</t>
+          <t>251381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>276114</t>
+          <t>277285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21737</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47333</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68954</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63386</t>
+          <t>66375</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103556</t>
+          <t>105853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37204</t>
+          <t>37237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>62578</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73808</t>
+          <t>73590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107075</t>
+          <t>106429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>155185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180538</t>
+          <t>180402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>244988</t>
+          <t>242975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>479743</t>
+          <t>480926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>524906</t>
+          <t>527392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>520163</t>
+          <t>518616</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577324</t>
+          <t>575470</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1014392</t>
+          <t>1011740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1091476</t>
+          <t>1088377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
